--- a/data/current/S_Curve_Dashboard_Source.xlsx
+++ b/data/current/S_Curve_Dashboard_Source.xlsx
@@ -517,7 +517,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-05-22 12:53:12</t>
+          <t>2026-05-25 16:04:00</t>
         </is>
       </c>
     </row>

--- a/data/current/S_Curve_Dashboard_Source.xlsx
+++ b/data/current/S_Curve_Dashboard_Source.xlsx
@@ -517,7 +517,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25 16:04:00</t>
+          <t>2026-05-22 12:53:12</t>
         </is>
       </c>
     </row>

--- a/data/current/S_Curve_Dashboard_Source.xlsx
+++ b/data/current/S_Curve_Dashboard_Source.xlsx
@@ -517,7 +517,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15 16:42:14</t>
+          <t>2026-06-15 16:47:23</t>
         </is>
       </c>
     </row>
